--- a/artfynd/A 39073-2019 artfynd.xlsx
+++ b/artfynd/A 39073-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 39073-2019 artfynd.xlsx
+++ b/artfynd/A 39073-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1918,117 +1918,6 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>114461498</v>
-      </c>
-      <c r="B12" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>sydost Buckarby, Upl</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>612588</v>
-      </c>
-      <c r="R12" t="n">
-        <v>6674777</v>
-      </c>
-      <c r="S12" t="n">
-        <v>10</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Uppsala</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Heby</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Uppland</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Nora</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>C-Heb-0299</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2018-10-31</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2018-10-31</t>
-        </is>
-      </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>Ingvar Sundh</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>Olof Hedgren</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
